--- a/excel/pacifico-ayacucho_efectivos.xlsx
+++ b/excel/pacifico-ayacucho_efectivos.xlsx
@@ -563,12 +563,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C001031427</t>
+          <t>C001461714</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>C001031427 - COLLADO VDA.DE ARCOCCAULLA ALEJANDRA</t>
+          <t>C001461714 - MEDRANO JURAHUA MARIA LUZ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -640,12 +640,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C001461714</t>
+          <t>C001473641</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>C001461714 - MEDRANO JURAHUA MARIA LUZ</t>
+          <t>C001473641 - QUISPE JANAMPA YUDITH PAOLA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C001669264</t>
+          <t>C000921781</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>C001669264 - DAVALOS PALOMINO EDGAR HERNAN</t>
+          <t>C000921781 - MENESES MENDIETA IRMA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
@@ -740,12 +740,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -755,9 +755,21 @@
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Mejor experiencia con la app</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -782,12 +794,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>C001711514</t>
+          <t>C001381669</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>C001711514 - HURTADO RIVERA ROSA ISABEL</t>
+          <t>C001381669 - CARDENAS CCENTI MIRIAM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -810,7 +822,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -847,17 +859,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>C001219345</t>
+          <t>C001711514</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C001219345 - ALVITEZ TACO IRMA</t>
+          <t>C001711514 - HURTADO RIVERA ROSA ISABEL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
@@ -870,12 +882,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -885,21 +897,9 @@
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -924,12 +924,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>C000921781</t>
+          <t>C001219345</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C000921781 - MENESES MENDIETA IRMA</t>
+          <t>C001219345 - ALVITEZ TACO IRMA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>C001381669</t>
+          <t>C000920373</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C001381669 - CARDENAS CCENTI MIRIAM</t>
+          <t>C000920373 - GALINDO POMA ANA YOLANDA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -1039,9 +1039,21 @@
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1066,12 +1078,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>C001750377</t>
+          <t>C001640679</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>C001750377 - MULTISERVICIOS VIECAL S.A.C.</t>
+          <t>C001640679 - YUPANQUI QUISPE LOURDES</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1116,7 +1128,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
     </row>
@@ -1143,17 +1155,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>C000920373</t>
+          <t>C001633485</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>C000920373 - GALINDO POMA ANA YOLANDA</t>
+          <t>C001633485 - FLORES PIRCA OLGA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
@@ -1166,12 +1178,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -1181,21 +1193,9 @@
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>C001473641</t>
+          <t>C001155650</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>C001473641 - QUISPE JANAMPA YUDITH PAOLA</t>
+          <t>C001155650 - PEREZ LLACCTAHUAMAN DELIA LEONILDA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>C001217185</t>
+          <t>C001031427</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>C001217185 - HUARANCCA GARCIA OLGA</t>
+          <t>C001031427 - COLLADO VDA.DE ARCOCCAULLA ALEJANDRA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>C001491694</t>
+          <t>C001217185</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>C001491694 - SOTACURO MUÑOZ ALBINA</t>
+          <t>C001217185 - HUARANCCA GARCIA OLGA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
@@ -1397,12 +1397,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1412,9 +1412,21 @@
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1439,17 +1451,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>C001640679</t>
+          <t>C001491694</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C001640679 - YUPANQUI QUISPE LOURDES</t>
+          <t>C001491694 - SOTACURO MUÑOZ ALBINA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
@@ -1462,12 +1474,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1477,21 +1489,9 @@
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Mejor experiencia con la app</t>
-        </is>
-      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1516,17 +1516,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>C001633485</t>
+          <t>C001687768</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C001633485 - FLORES PIRCA OLGA</t>
+          <t>C001687768 - URBINA FLORES MARIA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
@@ -1539,12 +1539,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1554,9 +1554,21 @@
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1581,17 +1593,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>C001155650</t>
+          <t>C001669264</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>C001155650 - PEREZ LLACCTAHUAMAN DELIA LEONILDA</t>
+          <t>C001669264 - DAVALOS PALOMINO EDGAR HERNAN</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
@@ -1604,12 +1616,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1619,21 +1631,9 @@
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>C004182546</t>
+          <t>C001753797</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C004182546 - PRADO ROCA EDITH</t>
+          <t>C001753797 - BARBOZA BASTIDAS EDITA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -1735,12 +1735,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>C004186439</t>
+          <t>C001668200</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C004186439 - FLORES ALBITES JUANA</t>
+          <t>C001668200 - LLANTOY HUAMAN MIRIAM MARGOT</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -1812,17 +1812,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>C004160953</t>
+          <t>C004182546</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>C004160953 - PALOMINO JANAMPA RAYDA</t>
+          <t>C004182546 - PRADO ROCA EDITH</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1850,9 +1850,21 @@
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Mejor experiencia con la app</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1877,12 +1889,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>C001753797</t>
+          <t>C001669740</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>C001753797 - BARBOZA BASTIDAS EDITA</t>
+          <t>C001669740 - JANAMPA GALINDO FLORA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1927,7 +1939,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
     </row>
@@ -1954,17 +1966,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>C001668200</t>
+          <t>C001748093</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>C001668200 - LLANTOY HUAMAN MIRIAM MARGOT</t>
+          <t>C001748093 - LLAMOCCA QUISPE JUAN</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
@@ -1977,12 +1989,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1992,21 +2004,9 @@
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>C001687768</t>
+          <t>C001750377</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C001687768 - URBINA FLORES MARIA DEL ROSARIO</t>
+          <t>C001750377 - MULTISERVICIOS VIECAL S.A.C.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -2108,12 +2108,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>C001669740</t>
+          <t>C004189005</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>C001669740 - JANAMPA GALINDO FLORA</t>
+          <t>C004189005 - TAIPE CRUZ ELIZABETH</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2185,17 +2185,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>C001748093</t>
+          <t>C004186439</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>C001748093 - LLAMOCCA QUISPE JUAN</t>
+          <t>C004186439 - FLORES ALBITES JUANA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
@@ -2208,12 +2208,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -2223,9 +2223,21 @@
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2250,17 +2262,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>C004189005</t>
+          <t>C004160953</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>C004189005 - TAIPE CRUZ ELIZABETH</t>
+          <t>C004160953 - PALOMINO JANAMPA RAYDA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
@@ -2273,12 +2285,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -2288,21 +2300,9 @@
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>Mejor experiencia con la app</t>
-        </is>
-      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>C004187301</t>
+          <t>C004185791</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C004187301 - MENDEZ HUAMAN YANINA</t>
+          <t>C004185791 - ZANABRIA DURAND ROSA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3008,17 +3008,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>C001666573</t>
+          <t>C004187301</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>C001666573 - JUSCAMAITA NOA LUIS BREYSIS</t>
+          <t>C004187301 - MENDEZ HUAMAN YANINA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
@@ -3031,12 +3031,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -3046,9 +3046,21 @@
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3073,12 +3085,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>C001564006</t>
+          <t>C004187315</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>C001564006 - BELLIDO BAUTISTA EDMUNDO</t>
+          <t>C004187315 - ESPINO YARANGA HONORIA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3150,17 +3162,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>C001198370</t>
+          <t>C001763764</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>C001198370 - GUTIERREZ CERDA NORY</t>
+          <t>C001763764 - GONZALES MORALES LUCIA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
@@ -3173,12 +3185,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado Definitivamente</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -3188,21 +3200,9 @@
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3227,12 +3227,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>C001729117</t>
+          <t>C004168930</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>C001729117 - DE LA CRUZ FLORES ELSA ANTONIA</t>
+          <t>C004168930 - GUTIERREZ PRADO ROSA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -3304,17 +3304,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>C004187315</t>
+          <t>C001666573</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>C004187315 - ESPINO YARANGA HONORIA</t>
+          <t>C001666573 - JUSCAMAITA NOA LUIS BREYSIS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
@@ -3327,12 +3327,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -3342,21 +3342,9 @@
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3381,12 +3369,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>C004168930</t>
+          <t>C001564006</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>C004168930 - GUTIERREZ PRADO ROSA</t>
+          <t>C001564006 - BELLIDO BAUTISTA EDMUNDO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3458,12 +3446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>C001763844</t>
+          <t>C001724460</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>C001763844 - REVOLLAR HUAMAN ROQUE</t>
+          <t>C001724460 - TINCO MENDOZA ANA KARINA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3535,12 +3523,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>C000922061</t>
+          <t>C001198370</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>C000922061 - ROMERO RUIZ VILMA</t>
+          <t>C001198370 - GUTIERREZ CERDA NORY</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3612,12 +3600,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>C001663749</t>
+          <t>C001729117</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>C001663749 - VEGA MENDOZA UBER ANTENOR</t>
+          <t>C001729117 - DE LA CRUZ FLORES ELSA ANTONIA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3662,7 +3650,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -3689,12 +3677,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>C001640455</t>
+          <t>C001557392</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>C001640455 - TAYPE ÑUFLO NERY</t>
+          <t>C001557392 - FLORES TAYPE JOHANA LISSET</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3739,7 +3727,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -3766,17 +3754,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>C001763764</t>
+          <t>C001475324</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>C001763764 - GONZALES MORALES LUCIA</t>
+          <t>C001475324 - RICHARTE CEBRIAN MARIA YSABEL</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
@@ -3789,12 +3777,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>PDV Cerrado Definitivamente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -3804,9 +3792,21 @@
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3831,17 +3831,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>C001475324</t>
+          <t>C001198368</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>C001475324 - RICHARTE CEBRIAN MARIA YSABEL</t>
+          <t>C001198368 - HUAYTALLA GODOY FELICITAS JUSTINA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H46" s="2" t="n">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado Definitivamente</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -3869,21 +3869,9 @@
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3908,17 +3896,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>C001198368</t>
+          <t>C001663749</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>C001198368 - HUAYTALLA GODOY FELICITAS JUSTINA</t>
+          <t>C001663749 - VEGA MENDOZA UBER ANTENOR</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H47" s="2" t="n">
@@ -3931,12 +3919,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>PDV Cerrado Definitivamente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -3946,9 +3934,21 @@
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Mejor experiencia con la app</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>C004185791</t>
+          <t>C001763844</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>C004185791 - ZANABRIA DURAND ROSA</t>
+          <t>C001763844 - REVOLLAR HUAMAN ROQUE</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>C001447727</t>
+          <t>C001640455</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>C001447727 - QUISPE CARRASCO MARGOT</t>
+          <t>C001640455 - TAYPE ÑUFLO NERY</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -4127,12 +4127,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>C001475217</t>
+          <t>C001447727</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>C001475217 - CAMPOS COLOS AGUSTINA</t>
+          <t>C001447727 - QUISPE CARRASCO MARGOT</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -4204,12 +4204,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>C001557392</t>
+          <t>C001475217</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>C001557392 - FLORES TAYPE JOHANA LISSET</t>
+          <t>C001475217 - CAMPOS COLOS AGUSTINA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>C001724460</t>
+          <t>C000921432</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>C001724460 - TINCO MENDOZA ANA KARINA</t>
+          <t>C000921432 - PASTOR RUA BETTY LILIANA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4358,12 +4358,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>C000921432</t>
+          <t>C000922061</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>C000921432 - PASTOR RUA BETTY LILIANA</t>
+          <t>C000922061 - ROMERO RUIZ VILMA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5015,12 +5015,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>C000922381</t>
+          <t>C001550439</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>C000922381 - LOPEZ ALIAGA DE ARENAS MIRIAM YANINA</t>
+          <t>C001550439 - TAIPE LLANTO NOEMI</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>C000920586</t>
+          <t>C001583705</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>C000920586 - QUISPE DE ARESTEGUI LIDIA</t>
+          <t>C001583705 - GUZMAN PALACIOS GLORIA BRIGITH</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>C001550439</t>
+          <t>C000920586</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>C001550439 - TAIPE LLANTO NOEMI</t>
+          <t>C000920586 - QUISPE DE ARESTEGUI LIDIA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -5246,12 +5246,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>C001583705</t>
+          <t>C001115126</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>C001583705 - GUZMAN PALACIOS GLORIA BRIGITH</t>
+          <t>C001115126 - MACHACA  SATURNINA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -5323,17 +5323,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>C000921479</t>
+          <t>C000921477</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>C000921479 - CUYA PRADO GLADYS</t>
+          <t>C000921477 - AYALA VASQUEZ ADELAIDA EMILIANA</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H66" s="2" t="n">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -5361,21 +5361,9 @@
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5400,12 +5388,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>C001412859</t>
+          <t>C000922381</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>C001412859 - MALLMA LOZANO JUANA VICTORIA</t>
+          <t>C000922381 - LOPEZ ALIAGA DE ARENAS MIRIAM YANINA</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5450,7 +5438,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -5477,12 +5465,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>C001533449</t>
+          <t>C000921479</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>C001533449 - RODRIGUEZ LOPEZ GLORIA</t>
+          <t>C000921479 - CUYA PRADO GLADYS</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5554,12 +5542,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>C001115126</t>
+          <t>C001385573</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>C001115126 - MACHACA  SATURNINA</t>
+          <t>C001385573 - LLANTOY HUAMAN MARLENY YANET</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5631,17 +5619,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>C000921477</t>
+          <t>C000920583</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>C000921477 - AYALA VASQUEZ ADELAIDA EMILIANA</t>
+          <t>C000920583 - CURI RIVEROS JUANA</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H70" s="2" t="n">
@@ -5654,12 +5642,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -5669,9 +5657,21 @@
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Mejor experiencia con la app</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5696,12 +5696,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>C001385573</t>
+          <t>C000920651</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>C001385573 - LLANTOY HUAMAN MARLENY YANET</t>
+          <t>C000920651 - ONCEBAY PARIONA ALEJANDRINA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -5773,12 +5773,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>C000920583</t>
+          <t>C000922487</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>C000920583 - CURI RIVEROS JUANA</t>
+          <t>C000922487 - PARADO QUISPE FLORABEL</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>C000920651</t>
+          <t>C001713624</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>C000920651 - ONCEBAY PARIONA ALEJANDRINA</t>
+          <t>C001713624 - ANAYA QUISPE MARLENE</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -5927,12 +5927,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>C000922487</t>
+          <t>C001412859</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>C000922487 - PARADO QUISPE FLORABEL</t>
+          <t>C001412859 - MALLMA LOZANO JUANA VICTORIA</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -6004,12 +6004,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>C001713624</t>
+          <t>C001533449</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>C001713624 - ANAYA QUISPE MARLENE</t>
+          <t>C001533449 - RODRIGUEZ LOPEZ GLORIA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -6081,12 +6081,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>C001549867</t>
+          <t>C001643213</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>C001549867 - TAIPE LLANTO NOEMI</t>
+          <t>C001643213 - ARANGO FERNANDEZ GABRIELA</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>C001617091</t>
+          <t>C001684339</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>C001617091 - CAMPOS CURI SILVIA</t>
+          <t>C001684339 - ROSALES ILLACCANQUI EDELMIRA SALOME</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -6235,12 +6235,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>C001684339</t>
+          <t>C001617091</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>C001684339 - ROSALES ILLACCANQUI EDELMIRA SALOME</t>
+          <t>C001617091 - CAMPOS CURI SILVIA</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -6285,7 +6285,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>C001643213</t>
+          <t>C001549867</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>C001643213 - ARANGO FERNANDEZ GABRIELA</t>
+          <t>C001549867 - TAIPE LLANTO NOEMI</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>C004167919</t>
+          <t>C001723407</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>C004167919 - SICHA HACHA FELIPE</t>
+          <t>C001723407 - CONTRERAS ÑAÑACC-HUARI TANIA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -6466,12 +6466,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>C004181104</t>
+          <t>C000920604</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>C004181104 - IÑAUSI ARONI MARIVEL</t>
+          <t>C000920604 - QUISPE DE HUARANCCAY DONATILDA N.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6543,17 +6543,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>C004160956</t>
+          <t>C001763687</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>C004160956 - YAURI PARIONA EDITH</t>
+          <t>C001763687 - CARHUAS ZANABRIA OLINDA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H82" s="2" t="n">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -6581,21 +6581,9 @@
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6620,12 +6608,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>C001723407</t>
+          <t>C004160956</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>C001723407 - CONTRERAS ÑAÑACC-HUARI TANIA</t>
+          <t>C004160956 - YAURI PARIONA EDITH</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6670,7 +6658,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -6697,17 +6685,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>C001763687</t>
+          <t>C004181104</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>C001763687 - CARHUAS ZANABRIA OLINDA</t>
+          <t>C004181104 - IÑAUSI ARONI MARIVEL</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H84" s="2" t="n">
@@ -6720,12 +6708,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -6735,9 +6723,21 @@
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>C000920604</t>
+          <t>C004167919</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>C000920604 - QUISPE DE HUARANCCAY DONATILDA N.</t>
+          <t>C004167919 - SICHA HACHA FELIPE</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -6839,12 +6839,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>C001730724</t>
+          <t>C004171791</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>C001730724 - GOMEZ MEDINA OLGA MARLENY</t>
+          <t>C004171791 - ZAVALETA HUAMAN YANET</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -6916,17 +6916,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>C001766379</t>
+          <t>C004159607</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>C001766379 - POMA TAQUIRI ILDA</t>
+          <t>C004159607 - BURGA QUICHCA LISBETH ANGELA</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H87" s="2" t="n">
@@ -6939,12 +6939,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -6954,9 +6954,21 @@
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6981,17 +6993,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>C004159607</t>
+          <t>C004040102</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>C004159607 - BURGA QUICHCA LISBETH ANGELA</t>
+          <t>C004040102 - ROJAS GUILLEN EDY</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H88" s="2" t="n">
@@ -7004,12 +7016,12 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
@@ -7019,21 +7031,9 @@
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7058,17 +7058,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>C004040102</t>
+          <t>C001730724</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>C004040102 - ROJAS GUILLEN EDY</t>
+          <t>C001730724 - GOMEZ MEDINA OLGA MARLENY</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H89" s="2" t="n">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
@@ -7096,9 +7096,21 @@
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7123,17 +7135,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>C004171791</t>
+          <t>C001766379</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>C004171791 - ZAVALETA HUAMAN YANET</t>
+          <t>C001766379 - POMA TAQUIRI ILDA</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H90" s="2" t="n">
@@ -7146,12 +7158,12 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -7161,21 +7173,9 @@
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7200,17 +7200,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>C001434983</t>
+          <t>C001623885</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>C001434983 - MENDOZA CORDOVA BERTHA</t>
+          <t>C001623885 - PALOMINO RODRIGUEZ DARWIN ANSHELMO</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H91" s="2" t="n">
@@ -7223,12 +7223,12 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -7238,9 +7238,21 @@
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7265,17 +7277,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>C001673891</t>
+          <t>C001632867</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>C001673891 - QUISPE PALOMINO DIANA</t>
+          <t>C001632867 - CALLE QUISPE EDUARDO</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H92" s="2" t="n">
@@ -7288,12 +7300,12 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -7303,9 +7315,21 @@
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7330,17 +7354,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>C001168800</t>
+          <t>C001668427</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>C001168800 - CARDENAS REYES MARTHA IRENE</t>
+          <t>C001668427 - RAMIREZ MAÑUICO KARINA</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H93" s="2" t="n">
@@ -7353,12 +7377,12 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -7368,9 +7392,21 @@
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7395,12 +7431,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>C001538020</t>
+          <t>C001631125</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>C001538020 - YAURI QUISPE CIRILA</t>
+          <t>C001631125 - ATAUQUI SULCA LUZMILA</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7445,7 +7481,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -7472,17 +7508,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>C001631125</t>
+          <t>C001168800</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>C001631125 - ATAUQUI SULCA LUZMILA</t>
+          <t>C001168800 - CARDENAS REYES MARTHA IRENE</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H95" s="2" t="n">
@@ -7495,12 +7531,12 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -7510,21 +7546,9 @@
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7549,12 +7573,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>C001632867</t>
+          <t>C001538020</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>C001632867 - CALLE QUISPE EDUARDO</t>
+          <t>C001538020 - YAURI QUISPE CIRILA</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7599,7 +7623,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -7626,17 +7650,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>C001668427</t>
+          <t>C001673891</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>C001668427 - RAMIREZ MAÑUICO KARINA</t>
+          <t>C001673891 - QUISPE PALOMINO DIANA</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H97" s="2" t="n">
@@ -7649,12 +7673,12 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -7664,21 +7688,9 @@
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7703,17 +7715,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>C001623885</t>
+          <t>C001568926</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>C001623885 - PALOMINO RODRIGUEZ DARWIN ANSHELMO</t>
+          <t>C001568926 - MULLO SULCA FELICITAS</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H98" s="2" t="n">
@@ -7726,12 +7738,12 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -7741,21 +7753,9 @@
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7780,17 +7780,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>C000921537</t>
+          <t>C001434983</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>C000921537 - ARANGO QUISPE EDITA</t>
+          <t>C001434983 - MENDOZA CORDOVA BERTHA</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H99" s="2" t="n">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -7818,21 +7818,9 @@
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q99" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7857,17 +7845,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>C001161670</t>
+          <t>C000921537</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>C001161670 - SULCA ALVITES MARIA CRISTINA</t>
+          <t>C000921537 - ARANGO QUISPE EDITA</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H100" s="2" t="n">
@@ -7880,12 +7868,12 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>PDV Cerrado Definitivamente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -7895,9 +7883,21 @@
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7922,17 +7922,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>C001703888</t>
+          <t>C001161670</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>C001703888 - FLORES BARBOZA MARTHA</t>
+          <t>C001161670 - SULCA ALVITES MARIA CRISTINA</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H101" s="2" t="n">
@@ -7945,12 +7945,12 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado Definitivamente</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
@@ -7960,21 +7960,9 @@
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q101" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8076,17 +8064,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>C001568926</t>
+          <t>C000920444</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>C001568926 - MULLO SULCA FELICITAS</t>
+          <t>C000920444 - QUISPE CONTRERAS RENEE</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H103" s="2" t="n">
@@ -8099,12 +8087,12 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -8114,9 +8102,21 @@
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>C000920444</t>
+          <t>C001703888</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>C000920444 - QUISPE CONTRERAS RENEE</t>
+          <t>C001703888 - FLORES BARBOZA MARTHA</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -8218,12 +8218,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>C001509217</t>
+          <t>C001469477</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>C001509217 - ARANA PALOMINO BERTHA MAGDALENA</t>
+          <t>C001469477 - GONZALEZ DE GOMEZ ROSA NETTA</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>C001469477</t>
+          <t>C001376881</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>C001469477 - GONZALEZ DE GOMEZ ROSA NETTA</t>
+          <t>C001376881 - OCHOA SAUÑE GLADYS ANHELA</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -8340,12 +8340,12 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -8372,12 +8372,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>C001376881</t>
+          <t>C001509217</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>C001376881 - OCHOA SAUÑE GLADYS ANHELA</t>
+          <t>C001509217 - ARANA PALOMINO BERTHA MAGDALENA</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>C004184774</t>
+          <t>C004202371</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>C004184774 - ESCALANTE HUAMAN FLORA</t>
+          <t>C004202371 - QUISPE GALINDO GABRIEL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8887,12 +8887,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>C004202371</t>
+          <t>C004184774</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>C004202371 - QUISPE GALINDO GABRIEL</t>
+          <t>C004184774 - ESCALANTE HUAMAN FLORA</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8964,17 +8964,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>C000922540</t>
+          <t>C000920871</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>C000922540 - BAUTISTA BEDRINANA GREGORIO</t>
+          <t>C000920871 - FERNANDEZ MUNAYLLA CIPRIANA</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H115" s="2" t="n">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>No es titular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L115" t="inlineStr"/>
@@ -9002,9 +9002,21 @@
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="inlineStr"/>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>Mejor experiencia con la app</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -9029,17 +9041,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>C001216296</t>
+          <t>C000922540</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>C001216296 - DE LA CRUZ VASQUEZ HILDA</t>
+          <t>C000922540 - BAUTISTA BEDRINANA GREGORIO</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H116" s="2" t="n">
@@ -9052,12 +9064,12 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No es titular</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
@@ -9067,21 +9079,9 @@
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q116" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>C001225337</t>
+          <t>C001216296</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>C001225337 - VENTURA FLORES ZENOBIA</t>
+          <t>C001216296 - DE LA CRUZ VASQUEZ HILDA</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>C000920871</t>
+          <t>C001225337</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>C000920871 - FERNANDEZ MUNAYLLA CIPRIANA</t>
+          <t>C001225337 - VENTURA FLORES ZENOBIA</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -9337,12 +9337,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>C001510421</t>
+          <t>C001215714</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>C001510421 - CANCHO PINEDO DORIS ESTHER</t>
+          <t>C001215714 - GUTIERREZ LAZARO YOVANA MARGOTH</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -9414,12 +9414,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>C000921953</t>
+          <t>C001418793</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>C000921953 - TENORIO ALARCON YOLANDA</t>
+          <t>C001418793 - YANCCE RUIZ FIDENCIANA</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -9491,12 +9491,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>C001418793</t>
+          <t>C000921953</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>C001418793 - YANCCE RUIZ FIDENCIANA</t>
+          <t>C000921953 - TENORIO ALARCON YOLANDA</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
     </row>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>C001215714</t>
+          <t>C001510421</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>C001215714 - GUTIERREZ LAZARO YOVANA MARGOTH</t>
+          <t>C001510421 - CANCHO PINEDO DORIS ESTHER</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -9710,12 +9710,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>C001225339</t>
+          <t>C001672279</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>C001225339 - MENESES YANCE HERLINDA</t>
+          <t>C001672279 - CONDE QUISPE VICENTA</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>C001403702</t>
+          <t>C001663639</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>C001403702 - QUINTO BARRIOS GABRIELA</t>
+          <t>C001663639 - QUISPE VENTURA FIDELA</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>C001669488</t>
+          <t>C001646412</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>C001669488 - SACCATOMA ANDIA EFRAIN CAYO</t>
+          <t>C001646412 - SOTO PRADO PAULINA</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9941,12 +9941,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>C001650062</t>
+          <t>C001225339</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>C001650062 - MENESES CALLAÑAUPA GRACIELA</t>
+          <t>C001225339 - MENESES YANCE HERLINDA</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -10018,17 +10018,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>C001643671</t>
+          <t>C001403702</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>C001643671 - AMBIA LLACCTAS ADELINA</t>
+          <t>C001403702 - QUINTO BARRIOS GABRIELA</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H129" s="2" t="n">
@@ -10041,12 +10041,12 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -10056,9 +10056,21 @@
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="inlineStr"/>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -10083,17 +10095,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>C001696477</t>
+          <t>C001643671</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>C001696477 - MAURICIO HUAMAN BETSIBEL</t>
+          <t>C001643671 - AMBIA LLACCTAS ADELINA</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H130" s="2" t="n">
@@ -10106,12 +10118,12 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
@@ -10121,21 +10133,9 @@
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P130" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q130" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>C001663639</t>
+          <t>C001745836</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>C001663639 - QUISPE VENTURA FIDELA</t>
+          <t>C001745836 - JAYO HUAMANI REYNA REGINA</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -10237,12 +10237,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>C001672279</t>
+          <t>C001650062</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>C001672279 - CONDE QUISPE VICENTA</t>
+          <t>C001650062 - MENESES CALLAÑAUPA GRACIELA</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>C001646412</t>
+          <t>C001721644</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>C001646412 - SOTO PRADO PAULINA</t>
+          <t>C001721644 - CURO REYES ROXANA</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -10391,17 +10391,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>C004167916</t>
+          <t>C001766607</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>C004167916 - GONZALES GONZALES YOLANDA</t>
+          <t>C001766607 - CORDERO MARTINEZ OLINDA</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H134" s="2" t="n">
@@ -10414,12 +10414,12 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Cambio de Giro</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L134" t="inlineStr"/>
@@ -10429,9 +10429,21 @@
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
-      <c r="Q134" t="inlineStr"/>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -10456,12 +10468,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>C004182533</t>
+          <t>C001730310</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>C004182533 - HUERTAS ARANGO LARRY</t>
+          <t>C001730310 - PALOMINO PRADO EMELYN ESTEFANI</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -10533,17 +10545,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>C004101278</t>
+          <t>C001730065</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>C004101278 - PRADO LEON MARIA MAGDALENA</t>
+          <t>C001730065 - AGUILAR GUILLEN BERTHA</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H136" s="2" t="n">
@@ -10556,12 +10568,12 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado Definitivamente</t>
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
@@ -10571,21 +10583,9 @@
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P136" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q136" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -10610,17 +10610,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>C001730065</t>
+          <t>C001669488</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>C001730065 - AGUILAR GUILLEN BERTHA</t>
+          <t>C001669488 - SACCATOMA ANDIA EFRAIN CAYO</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H137" s="2" t="n">
@@ -10633,12 +10633,12 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>PDV Cerrado Definitivamente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L137" t="inlineStr"/>
@@ -10648,9 +10648,21 @@
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="inlineStr"/>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -10675,17 +10687,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>C004054716</t>
+          <t>C001696477</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>C004054716 - ORIUNDO PALOMINO MAYRA SENAIDA</t>
+          <t>C001696477 - MAURICIO HUAMAN BETSIBEL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H138" s="2" t="n">
@@ -10698,12 +10710,12 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L138" t="inlineStr"/>
@@ -10713,9 +10725,21 @@
         </is>
       </c>
       <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="inlineStr"/>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -10740,17 +10764,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>C001721644</t>
+          <t>C004054716</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>C001721644 - CURO REYES ROXANA</t>
+          <t>C004054716 - ORIUNDO PALOMINO MAYRA SENAIDA</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H139" s="2" t="n">
@@ -10763,12 +10787,12 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L139" t="inlineStr"/>
@@ -10778,21 +10802,9 @@
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P139" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q139" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -10817,12 +10829,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>C001766607</t>
+          <t>C004182533</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>C001766607 - CORDERO MARTINEZ OLINDA</t>
+          <t>C004182533 - HUERTAS ARANGO LARRY</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10867,7 +10879,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10906,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>C001730310</t>
+          <t>C004101278</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>C001730310 - PALOMINO PRADO EMELYN ESTEFANI</t>
+          <t>C004101278 - PRADO LEON MARIA MAGDALENA</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -10944,7 +10956,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -10971,17 +10983,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>C001745836</t>
+          <t>C004167916</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>C001745836 - JAYO HUAMANI REYNA REGINA</t>
+          <t>C004167916 - GONZALES GONZALES YOLANDA</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H142" s="2" t="n">
@@ -10994,12 +11006,12 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cambio de Giro</t>
         </is>
       </c>
       <c r="L142" t="inlineStr"/>
@@ -11009,21 +11021,9 @@
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P142" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q142" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -11048,12 +11048,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>C004060033</t>
+          <t>C004184765</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>C004060033 - LEON YANA ANGEL EDDU</t>
+          <t>C004184765 - HUAMAN MEJIA SULMA</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -11098,7 +11098,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -11125,17 +11125,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>C004048657</t>
+          <t>C004173522</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>C004048657 - YARANGA QUICANA ENAIDA MARIA</t>
+          <t>C004173522 - ROJAS TOVAR RICHARD AMIEL</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H144" s="2" t="n">
@@ -11148,12 +11148,12 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>No es titular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L144" t="inlineStr"/>
@@ -11163,9 +11163,21 @@
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr"/>
-      <c r="Q144" t="inlineStr"/>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -11190,12 +11202,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>C001735047</t>
+          <t>C004060033</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>C001735047 - RAMOS DE TACAS DIONISIA</t>
+          <t>C004060033 - LEON YANA ANGEL EDDU</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -11267,17 +11279,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>C004173522</t>
+          <t>C004048657</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>C004173522 - ROJAS TOVAR RICHARD AMIEL</t>
+          <t>C004048657 - YARANGA QUICANA ENAIDA MARIA</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H146" s="2" t="n">
@@ -11290,12 +11302,12 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No es titular</t>
         </is>
       </c>
       <c r="L146" t="inlineStr"/>
@@ -11305,21 +11317,9 @@
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
-      <c r="O146" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P146" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q146" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -11344,17 +11344,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>C004184765</t>
+          <t>C001766569</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>C004184765 - HUAMAN MEJIA SULMA</t>
+          <t>C001766569 - TINOCO AGUILAR JHONATAN</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H147" s="2" t="n">
@@ -11367,12 +11367,12 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cambio de Giro</t>
         </is>
       </c>
       <c r="L147" t="inlineStr"/>
@@ -11382,21 +11382,9 @@
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P147" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q147" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -11421,12 +11409,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>C004186428</t>
+          <t>C001751665</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>C004186428 - HUAMAN FERNANDEZ NELSABETT</t>
+          <t>C001751665 - VENTURA FERNANDEZ MARIA ELENA</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -11471,7 +11459,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11486,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>C001405716</t>
+          <t>C001735047</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>C001405716 - FERNANDEZ DE BAJALQUI CARMEN</t>
+          <t>C001735047 - RAMOS DE TACAS DIONISIA</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -11548,7 +11536,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -11575,12 +11563,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>C001503289</t>
+          <t>C001645963</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>C001503289 - ALFARO GUTIERREZ FLORINA</t>
+          <t>C001645963 - QUISPE CACERES FIORELA DEL PILAR</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11625,7 +11613,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -11652,12 +11640,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>C001645963</t>
+          <t>C001750370</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>C001645963 - QUISPE CACERES FIORELA DEL PILAR</t>
+          <t>C001750370 - RISCO MENTANA MILAGROS SOFIA</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -11729,12 +11717,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>C001750370</t>
+          <t>C001737770</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>C001750370 - RISCO MENTANA MILAGROS SOFIA</t>
+          <t>C001737770 - QUISPE CUBA ANATOLIA</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -11806,17 +11794,17 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>C001751665</t>
+          <t>C001674490</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>C001751665 - VENTURA FERNANDEZ MARIA ELENA</t>
+          <t>C001674490 - ESPINO MENDOZA IRMA</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H153" s="2" t="n">
@@ -11829,12 +11817,12 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L153" t="inlineStr"/>
@@ -11844,21 +11832,9 @@
         </is>
       </c>
       <c r="N153" t="inlineStr"/>
-      <c r="O153" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P153" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q153" t="inlineStr">
-        <is>
-          <t>Mejor experiencia con la app</t>
-        </is>
-      </c>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -11883,12 +11859,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>C001737770</t>
+          <t>C001704643</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>C001737770 - QUISPE CUBA ANATOLIA</t>
+          <t>C001704643 - HUAMANI DE CORDOVA PAULINA</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11933,7 +11909,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -12037,17 +12013,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>C001674490</t>
+          <t>C001405716</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>C001674490 - ESPINO MENDOZA IRMA</t>
+          <t>C001405716 - FERNANDEZ DE BAJALQUI CARMEN</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H156" s="2" t="n">
@@ -12060,12 +12036,12 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L156" t="inlineStr"/>
@@ -12075,9 +12051,21 @@
         </is>
       </c>
       <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
-      <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="inlineStr"/>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -12102,12 +12090,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>C001704643</t>
+          <t>C001503289</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>C001704643 - HUAMANI DE CORDOVA PAULINA</t>
+          <t>C001503289 - ALFARO GUTIERREZ FLORINA</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -12179,17 +12167,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>C001766569</t>
+          <t>C000921887</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>C001766569 - TINOCO AGUILAR JHONATAN</t>
+          <t>C000921887 - MENDOZA AUQUI TRINIDAD</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H158" s="2" t="n">
@@ -12202,12 +12190,12 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Cambio de Giro</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L158" t="inlineStr"/>
@@ -12217,9 +12205,21 @@
         </is>
       </c>
       <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr"/>
-      <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="inlineStr"/>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -12244,12 +12244,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>C000921887</t>
+          <t>C001563236</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>C000921887 - MENDOZA AUQUI TRINIDAD</t>
+          <t>C001563236 - TELLO CUADROS YENI</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -12321,12 +12321,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>C001563236</t>
+          <t>C004186418</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>C001563236 - TELLO CUADROS YENI</t>
+          <t>C004186418 - CHOCCE CURI CLAIDE CRISTINA</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -12398,12 +12398,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>C004186418</t>
+          <t>C004184772</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>C004186418 - CHOCCE CURI CLAIDE CRISTINA</t>
+          <t>C004184772 - COELLO ARANGO KARINA</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12475,12 +12475,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>C004184772</t>
+          <t>C004192068</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>C004184772 - COELLO ARANGO KARINA</t>
+          <t>C004192068 - CARRENO ALBURQUEQUE JUAN ISAIAS</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12552,12 +12552,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>C004192068</t>
+          <t>C004186423</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>C004192068 - CARRENO ALBURQUEQUE JUAN ISAIAS</t>
+          <t>C004186423 - QUISPE CERVANTES RAYDA VICTORIA</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -12629,12 +12629,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>C004186423</t>
+          <t>C004186428</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>C004186423 - QUISPE CERVANTES RAYDA VICTORIA</t>
+          <t>C004186428 - HUAMAN FERNANDEZ NELSABETT</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -13079,17 +13079,17 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>C001724257</t>
+          <t>C001729329</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>C001724257 - CANGANA MENDOZA WALTER DANIEL</t>
+          <t>C001729329 - DIAZ HUACHACA SEGUNDINA</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H170" s="2" t="n">
@@ -13102,12 +13102,12 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L170" t="inlineStr"/>
@@ -13117,9 +13117,21 @@
         </is>
       </c>
       <c r="N170" t="inlineStr"/>
-      <c r="O170" t="inlineStr"/>
-      <c r="P170" t="inlineStr"/>
-      <c r="Q170" t="inlineStr"/>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -13144,17 +13156,17 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>C001729329</t>
+          <t>C001724257</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>C001729329 - DIAZ HUACHACA SEGUNDINA</t>
+          <t>C001724257 - CANGANA MENDOZA WALTER DANIEL</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H171" s="2" t="n">
@@ -13167,12 +13179,12 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="L171" t="inlineStr"/>
@@ -13182,21 +13194,9 @@
         </is>
       </c>
       <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P171" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q171" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr"/>
+      <c r="Q171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>C001409403</t>
+          <t>C000920204</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>C001409403 - CRUZATT QUISPE EUGENIA SERAFINA</t>
+          <t>C000920204 - QUISPE LEON SOLEDAD</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -14020,12 +14020,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>C000920204</t>
+          <t>C001005085</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>C000920204 - QUISPE LEON SOLEDAD</t>
+          <t>C001005085 - JERI CHACHAYMA FELIX</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
@@ -14097,12 +14097,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>C001005085</t>
+          <t>C001412189</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>C001005085 - JERI CHACHAYMA FELIX</t>
+          <t>C001412189 - GARAMENDI QUISPE RODIL</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -14142,12 +14142,12 @@
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -14174,12 +14174,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>C001412189</t>
+          <t>C001749225</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>C001412189 - GARAMENDI QUISPE RODIL</t>
+          <t>C001749225 - QUISPE MUNOZ AMELDA</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -14251,12 +14251,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>C001749225</t>
+          <t>C000920240</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>C001749225 - QUISPE MUNOZ AMELDA</t>
+          <t>C000920240 - TUCTA MALDONADO ENRIQUETA</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -14328,12 +14328,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>C000920240</t>
+          <t>C001373985</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>C000920240 - TUCTA MALDONADO ENRIQUETA</t>
+          <t>C001373985 - CUNTO GONZALES VIRGINIA</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -14405,12 +14405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>C001373985</t>
+          <t>C001409403</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>C001373985 - CUNTO GONZALES VIRGINIA</t>
+          <t>C001409403 - CRUZATT QUISPE EUGENIA SERAFINA</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -15488,17 +15488,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>C004218737</t>
+          <t>C004098429</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>C004218737 - DISTRIBUIDORA LURESA E.I.R.L.</t>
+          <t>C004098429 - JAUREGUI FLORES LEYDA</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H203" s="2" t="n">
@@ -15511,12 +15511,12 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L203" t="inlineStr"/>
@@ -15526,21 +15526,9 @@
         </is>
       </c>
       <c r="N203" t="inlineStr"/>
-      <c r="O203" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P203" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q203" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="inlineStr"/>
+      <c r="Q203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -15695,17 +15683,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>C004098429</t>
+          <t>C001761755</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>C004098429 - JAUREGUI FLORES LEYDA</t>
+          <t>C001761755 - HUALLPA PUCLLA LUZMERY</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H206" s="2" t="n">
@@ -15718,12 +15706,12 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L206" t="inlineStr"/>
@@ -15733,9 +15721,21 @@
         </is>
       </c>
       <c r="N206" t="inlineStr"/>
-      <c r="O206" t="inlineStr"/>
-      <c r="P206" t="inlineStr"/>
-      <c r="Q206" t="inlineStr"/>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>C001761755</t>
+          <t>C004101499</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>C001761755 - HUALLPA PUCLLA LUZMERY</t>
+          <t>C004101499 - TINEO CCENHUA AMANDA</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -15810,7 +15810,7 @@
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -15837,12 +15837,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>C004101499</t>
+          <t>C004163224</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>C004101499 - TINEO CCENHUA AMANDA</t>
+          <t>C004163224 - HUAMAN CUETO KAHORY SIOMI NEYDA</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -15887,7 +15887,7 @@
       </c>
       <c r="Q208" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -15914,12 +15914,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>C004163224</t>
+          <t>C001744286</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>C004163224 - HUAMAN CUETO KAHORY SIOMI NEYDA</t>
+          <t>C001744286 - SOSA FLORES FELIX</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -15991,12 +15991,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>C001744286</t>
+          <t>C001729604</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>C001744286 - SOSA FLORES FELIX</t>
+          <t>C001729604 - CONGA VASQUEZ LUZ CLARITA</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -16041,7 +16041,7 @@
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
     </row>
@@ -16068,12 +16068,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>C001729604</t>
+          <t>C001722581</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>C001729604 - CONGA VASQUEZ LUZ CLARITA</t>
+          <t>C001722581 - HUYHUA CURO ILIANA</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -16145,12 +16145,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>C001722581</t>
+          <t>C004196903</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>C001722581 - HUYHUA CURO ILIANA</t>
+          <t>C004196903 - DIAZ GOMEZ MARTHA</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -16195,7 +16195,7 @@
       </c>
       <c r="Q212" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>C004196903</t>
+          <t>C004218737</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>C004196903 - DIAZ GOMEZ MARTHA</t>
+          <t>C004218737 - DISTRIBUIDORA LURESA E.I.R.L.</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -16272,7 +16272,7 @@
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -16376,12 +16376,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>C001530391</t>
+          <t>C000920856</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>C001530391 - CURI VELARDE JOHANNA DAISY</t>
+          <t>C000920856 - QUISPE GOMEZ VICTOR</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -16441,12 +16441,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>C000920856</t>
+          <t>C001530391</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>C000920856 - QUISPE GOMEZ VICTOR</t>
+          <t>C001530391 - CURI VELARDE JOHANNA DAISY</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -16506,17 +16506,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>C001565994</t>
+          <t>C001457999</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>C001565994 - INGA UCEDA LUZ DEL PILAR</t>
+          <t>C001457999 - BORDA ESPINO ROBERTA</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H217" s="2" t="n">
@@ -16529,12 +16529,12 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L217" t="inlineStr"/>
@@ -16544,9 +16544,21 @@
         </is>
       </c>
       <c r="N217" t="inlineStr"/>
-      <c r="O217" t="inlineStr"/>
-      <c r="P217" t="inlineStr"/>
-      <c r="Q217" t="inlineStr"/>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>Mejor experiencia con la app</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -16571,17 +16583,17 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>C001501806</t>
+          <t>C001565994</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>C001501806 - SANTIAGO BORDA LIDIA DIONISIA</t>
+          <t>C001565994 - INGA UCEDA LUZ DEL PILAR</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H218" s="2" t="n">
@@ -16594,12 +16606,12 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="L218" t="inlineStr"/>
@@ -16609,21 +16621,9 @@
         </is>
       </c>
       <c r="N218" t="inlineStr"/>
-      <c r="O218" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P218" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q218" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O218" t="inlineStr"/>
+      <c r="P218" t="inlineStr"/>
+      <c r="Q218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -16648,12 +16648,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>C001480509</t>
+          <t>C001501806</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>CHAUCA SIMON INELDA</t>
+          <t>C001501806 - SANTIAGO BORDA LIDIA DIONISIA</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -16698,7 +16698,7 @@
       </c>
       <c r="Q219" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -16725,12 +16725,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>C001568921</t>
+          <t>C001480509</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>C001568921 - HUARANCCAY ARANA NANCY</t>
+          <t>CHAUCA SIMON INELDA</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -16802,12 +16802,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>C001457999</t>
+          <t>C004048881</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>C001457999 - BORDA ESPINO ROBERTA</t>
+          <t>C004048881 - MORALES MORALES ENRIQUE</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -16852,7 +16852,7 @@
       </c>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -16879,17 +16879,17 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>C001724594</t>
+          <t>C001568921</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>C001724594 - VALENZUELA PILLIHUAMAN GLORIA</t>
+          <t>C001568921 - HUARANCCAY ARANA NANCY</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H222" s="2" t="n">
@@ -16902,12 +16902,12 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L222" t="inlineStr"/>
@@ -16917,9 +16917,21 @@
         </is>
       </c>
       <c r="N222" t="inlineStr"/>
-      <c r="O222" t="inlineStr"/>
-      <c r="P222" t="inlineStr"/>
-      <c r="Q222" t="inlineStr"/>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -17009,17 +17021,17 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>C004097118</t>
+          <t>C001724594</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>C004097118 - OCHANTE QUISPE DE FERNANDEZ SUSY ELSA</t>
+          <t>C001724594 - VALENZUELA PILLIHUAMAN GLORIA</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H224" s="2" t="n">
@@ -17032,12 +17044,12 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L224" t="inlineStr"/>
@@ -17047,21 +17059,9 @@
         </is>
       </c>
       <c r="N224" t="inlineStr"/>
-      <c r="O224" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P224" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q224" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O224" t="inlineStr"/>
+      <c r="P224" t="inlineStr"/>
+      <c r="Q224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -17086,17 +17086,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>C001665633</t>
+          <t>C004097118</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>C001665633 - QUISPE MENDOZA RETHEZ</t>
+          <t>C004097118 - OCHANTE QUISPE DE FERNANDEZ SUSY ELSA</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H225" s="2" t="n">
@@ -17109,12 +17109,12 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L225" t="inlineStr"/>
@@ -17124,9 +17124,21 @@
         </is>
       </c>
       <c r="N225" t="inlineStr"/>
-      <c r="O225" t="inlineStr"/>
-      <c r="P225" t="inlineStr"/>
-      <c r="Q225" t="inlineStr"/>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -17151,17 +17163,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>C001477518</t>
+          <t>C001665633</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>C001477518 - PILLACA LUJAN SONIA</t>
+          <t>C001665633 - QUISPE MENDOZA RETHEZ</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H226" s="2" t="n">
@@ -17174,12 +17186,12 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L226" t="inlineStr"/>
@@ -17189,21 +17201,9 @@
         </is>
       </c>
       <c r="N226" t="inlineStr"/>
-      <c r="O226" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P226" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q226" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" t="inlineStr"/>
+      <c r="Q226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -17228,17 +17228,17 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>C001622642</t>
+          <t>C001477518</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>C001622642 - JAYO RAMOS ROGER</t>
+          <t>C001477518 - PILLACA LUJAN SONIA</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H227" s="2" t="n">
@@ -17251,12 +17251,12 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L227" t="inlineStr"/>
@@ -17266,9 +17266,21 @@
         </is>
       </c>
       <c r="N227" t="inlineStr"/>
-      <c r="O227" t="inlineStr"/>
-      <c r="P227" t="inlineStr"/>
-      <c r="Q227" t="inlineStr"/>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -17370,17 +17382,17 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>C001632454</t>
+          <t>C001622642</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>C001632454 - ELME CARDENAS GRACIELA</t>
+          <t>C001622642 - JAYO RAMOS ROGER</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H229" s="2" t="n">
@@ -17393,12 +17405,12 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L229" t="inlineStr"/>
@@ -17408,21 +17420,9 @@
         </is>
       </c>
       <c r="N229" t="inlineStr"/>
-      <c r="O229" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P229" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q229" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="O229" t="inlineStr"/>
+      <c r="P229" t="inlineStr"/>
+      <c r="Q229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -17447,12 +17447,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>C004184360</t>
+          <t>C001632454</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>C004184360 - ROJAS GUTIERREZ MAGDALENA</t>
+          <t>C001632454 - ELME CARDENAS GRACIELA</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -17497,7 +17497,7 @@
       </c>
       <c r="Q230" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -17524,17 +17524,17 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>C004172917</t>
+          <t>C004184360</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>C004172917 - QUISPE DE LA CRUZ KEVIN JULIANO</t>
+          <t>C004184360 - ROJAS GUTIERREZ MAGDALENA</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H231" s="2" t="n">
@@ -17547,12 +17547,12 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L231" t="inlineStr"/>
@@ -17562,9 +17562,21 @@
         </is>
       </c>
       <c r="N231" t="inlineStr"/>
-      <c r="O231" t="inlineStr"/>
-      <c r="P231" t="inlineStr"/>
-      <c r="Q231" t="inlineStr"/>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>Mejor experiencia con la app</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -17589,17 +17601,17 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>C004187312</t>
+          <t>C004094777</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>C004187312 - MEDINA BUSTAMANTE ZENAIDA</t>
+          <t>C004094777 - RAMIREZ RAMOS CLARIZA</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H232" s="2" t="n">
@@ -17612,12 +17624,12 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L232" t="inlineStr"/>
@@ -17627,21 +17639,9 @@
         </is>
       </c>
       <c r="N232" t="inlineStr"/>
-      <c r="O232" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P232" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q232" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O232" t="inlineStr"/>
+      <c r="P232" t="inlineStr"/>
+      <c r="Q232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -17743,12 +17743,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>C001579492</t>
+          <t>C004172917</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>C001579492 - CHAVEZ VILLANO YUDIT</t>
+          <t>C004172917 - QUISPE DE LA CRUZ KEVIN JULIANO</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -17771,7 +17771,7 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L234" t="inlineStr"/>
@@ -17808,17 +17808,17 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>C001722355</t>
+          <t>C004187312</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>C001722355 - QUISPE CURACA DELIA CHARO</t>
+          <t>C004187312 - MEDINA BUSTAMANTE ZENAIDA</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H235" s="2" t="n">
@@ -17831,12 +17831,12 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L235" t="inlineStr"/>
@@ -17846,9 +17846,21 @@
         </is>
       </c>
       <c r="N235" t="inlineStr"/>
-      <c r="O235" t="inlineStr"/>
-      <c r="P235" t="inlineStr"/>
-      <c r="Q235" t="inlineStr"/>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -17873,12 +17885,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>C004094777</t>
+          <t>C001579492</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>C004094777 - RAMIREZ RAMOS CLARIZA</t>
+          <t>C001579492 - CHAVEZ VILLANO YUDIT</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -17938,12 +17950,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>C001006672</t>
+          <t>C001722355</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>C001006672 - GARCIA TOVAR NOEMI ADE</t>
+          <t>C001722355 - QUISPE CURACA DELIA CHARO</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -17966,7 +17978,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>PDV Cerrado Definitivamente</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L237" t="inlineStr"/>
@@ -18003,17 +18015,17 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>C004048881</t>
+          <t>C004054722</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>C004048881 - MORALES MORALES ENRIQUE</t>
+          <t>C004054722 - QUISPE RAMOS FLOR MARISOL</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H238" s="2" t="n">
@@ -18026,12 +18038,12 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cambio de Giro</t>
         </is>
       </c>
       <c r="L238" t="inlineStr"/>
@@ -18041,21 +18053,9 @@
         </is>
       </c>
       <c r="N238" t="inlineStr"/>
-      <c r="O238" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P238" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q238" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O238" t="inlineStr"/>
+      <c r="P238" t="inlineStr"/>
+      <c r="Q238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -18080,12 +18080,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>C004054722</t>
+          <t>C001006672</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>C004054722 - QUISPE RAMOS FLOR MARISOL</t>
+          <t>C001006672 - GARCIA TOVAR NOEMI ADE</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -18108,7 +18108,7 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>Cambio de Giro</t>
+          <t>PDV Cerrado Definitivamente</t>
         </is>
       </c>
       <c r="L239" t="inlineStr"/>
@@ -18595,12 +18595,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>C004187113</t>
+          <t>C004093406</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>C004187113 - ESPINOZA BUSTAMANTE MARIBEL</t>
+          <t>C004093406 - CARDENAS QUISPE GREICY YESENIA</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -18645,7 +18645,7 @@
       </c>
       <c r="Q246" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
     </row>
@@ -18672,12 +18672,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>C004093406</t>
+          <t>C004187113</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>C004093406 - CARDENAS QUISPE GREICY YESENIA</t>
+          <t>C004187113 - ESPINOZA BUSTAMANTE MARIBEL</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="Q247" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -19175,17 +19175,17 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>C004218114</t>
+          <t>C004188428</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>C004218114 - GAMBOA GUZMAN YGOR</t>
+          <t>C004188428 - TENORIO MORENO ELISA</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H254" s="2" t="n">
@@ -19198,12 +19198,12 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L254" t="inlineStr"/>
@@ -19213,21 +19213,9 @@
         </is>
       </c>
       <c r="N254" t="inlineStr"/>
-      <c r="O254" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P254" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q254" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O254" t="inlineStr"/>
+      <c r="P254" t="inlineStr"/>
+      <c r="Q254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -19252,17 +19240,17 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>C004188428</t>
+          <t>C004218114</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>C004188428 - TENORIO MORENO ELISA</t>
+          <t>C004218114 - GAMBOA GUZMAN YGOR</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H255" s="2" t="n">
@@ -19275,12 +19263,12 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L255" t="inlineStr"/>
@@ -19290,9 +19278,21 @@
         </is>
       </c>
       <c r="N255" t="inlineStr"/>
-      <c r="O255" t="inlineStr"/>
-      <c r="P255" t="inlineStr"/>
-      <c r="Q255" t="inlineStr"/>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -19317,17 +19317,17 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>C001014335</t>
+          <t>C000921973</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>C001014335 - RODRIGUEZ RAMOS VLADIMIR</t>
+          <t>C000921973 - TENORIO LLALLAHUI MIRIAN</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H256" s="2" t="n">
@@ -19340,12 +19340,12 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L256" t="inlineStr"/>
@@ -19355,9 +19355,21 @@
         </is>
       </c>
       <c r="N256" t="inlineStr"/>
-      <c r="O256" t="inlineStr"/>
-      <c r="P256" t="inlineStr"/>
-      <c r="Q256" t="inlineStr"/>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -19382,17 +19394,17 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>C000921973</t>
+          <t>C001446190</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>C000921973 - TENORIO LLALLAHUI MIRIAN</t>
+          <t>C001446190 - ANTICONA DIAZ ARNOLDE</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H257" s="2" t="n">
@@ -19405,12 +19417,12 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L257" t="inlineStr"/>
@@ -19420,21 +19432,9 @@
         </is>
       </c>
       <c r="N257" t="inlineStr"/>
-      <c r="O257" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P257" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q257" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O257" t="inlineStr"/>
+      <c r="P257" t="inlineStr"/>
+      <c r="Q257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -19459,12 +19459,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>C001446190</t>
+          <t>C001014335</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>C001446190 - ANTICONA DIAZ ARNOLDE</t>
+          <t>C001014335 - RODRIGUEZ RAMOS VLADIMIR</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -19487,7 +19487,7 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L258" t="inlineStr"/>
@@ -19524,17 +19524,17 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>C001664645</t>
+          <t>C001694729</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>C001664645 - ESPINOZA MITMA JULIA</t>
+          <t>C001694729 - FLORES PAQUIYAURI RICHARD</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H259" s="2" t="n">
@@ -19547,12 +19547,12 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L259" t="inlineStr"/>
@@ -19562,21 +19562,9 @@
         </is>
       </c>
       <c r="N259" t="inlineStr"/>
-      <c r="O259" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P259" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q259" t="inlineStr">
-        <is>
-          <t>Mejor experiencia con la app</t>
-        </is>
-      </c>
+      <c r="O259" t="inlineStr"/>
+      <c r="P259" t="inlineStr"/>
+      <c r="Q259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -19601,17 +19589,17 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>C001694729</t>
+          <t>C001664645</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>C001694729 - FLORES PAQUIYAURI RICHARD</t>
+          <t>C001664645 - ESPINOZA MITMA JULIA</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H260" s="2" t="n">
@@ -19624,12 +19612,12 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L260" t="inlineStr"/>
@@ -19639,9 +19627,21 @@
         </is>
       </c>
       <c r="N260" t="inlineStr"/>
-      <c r="O260" t="inlineStr"/>
-      <c r="P260" t="inlineStr"/>
-      <c r="Q260" t="inlineStr"/>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>Mejor experiencia con la app</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -19820,17 +19820,17 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>C001682302</t>
+          <t>C001016621</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>CALDERON GOMEZ SONIA</t>
+          <t>C001016621 - VEGA SULCA VICTOR ALFREDO</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H263" s="2" t="n">
@@ -19843,12 +19843,12 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L263" t="inlineStr"/>
@@ -19858,9 +19858,21 @@
         </is>
       </c>
       <c r="N263" t="inlineStr"/>
-      <c r="O263" t="inlineStr"/>
-      <c r="P263" t="inlineStr"/>
-      <c r="Q263" t="inlineStr"/>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -19885,17 +19897,17 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>C001016621</t>
+          <t>C001682302</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>C001016621 - VEGA SULCA VICTOR ALFREDO</t>
+          <t>CALDERON GOMEZ SONIA</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H264" s="2" t="n">
@@ -19908,12 +19920,12 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L264" t="inlineStr"/>
@@ -19923,21 +19935,9 @@
         </is>
       </c>
       <c r="N264" t="inlineStr"/>
-      <c r="O264" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P264" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q264" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O264" t="inlineStr"/>
+      <c r="P264" t="inlineStr"/>
+      <c r="Q264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -19962,17 +19962,17 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>C000921793</t>
+          <t>C001326474</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>C000921793 - CHURAMPI GONZALES JUAN JOSE</t>
+          <t>C001326474 - GUILLEN DE RAMIREZ REYNA MATILDE</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H265" s="2" t="n">
@@ -19985,12 +19985,12 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L265" t="inlineStr"/>
@@ -20000,9 +20000,21 @@
         </is>
       </c>
       <c r="N265" t="inlineStr"/>
-      <c r="O265" t="inlineStr"/>
-      <c r="P265" t="inlineStr"/>
-      <c r="Q265" t="inlineStr"/>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -20027,17 +20039,17 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>C001326474</t>
+          <t>C000921793</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>C001326474 - GUILLEN DE RAMIREZ REYNA MATILDE</t>
+          <t>C000921793 - CHURAMPI GONZALES JUAN JOSE</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H266" s="2" t="n">
@@ -20050,12 +20062,12 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L266" t="inlineStr"/>
@@ -20065,21 +20077,9 @@
         </is>
       </c>
       <c r="N266" t="inlineStr"/>
-      <c r="O266" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P266" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q266" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="O266" t="inlineStr"/>
+      <c r="P266" t="inlineStr"/>
+      <c r="Q266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -21608,17 +21608,17 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>C004101139</t>
+          <t>C004179981</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>C004101139 - VIMANE QUALITY S.A.C.</t>
+          <t>C004179981 - GOZME JANAMPA CLEMENTINA</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H287" s="2" t="n">
@@ -21631,12 +21631,12 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L287" t="inlineStr"/>
@@ -21646,9 +21646,21 @@
         </is>
       </c>
       <c r="N287" t="inlineStr"/>
-      <c r="O287" t="inlineStr"/>
-      <c r="P287" t="inlineStr"/>
-      <c r="Q287" t="inlineStr"/>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>Mejor experiencia con la app</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -21673,17 +21685,17 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>C004179981</t>
+          <t>C004101139</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>C004179981 - GOZME JANAMPA CLEMENTINA</t>
+          <t>C004101139 - VIMANE QUALITY S.A.C.</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H288" s="2" t="n">
@@ -21696,12 +21708,12 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L288" t="inlineStr"/>
@@ -21711,21 +21723,9 @@
         </is>
       </c>
       <c r="N288" t="inlineStr"/>
-      <c r="O288" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P288" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q288" t="inlineStr">
-        <is>
-          <t>Mejor experiencia con la app</t>
-        </is>
-      </c>
+      <c r="O288" t="inlineStr"/>
+      <c r="P288" t="inlineStr"/>
+      <c r="Q288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -25716,12 +25716,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>C004051583</t>
+          <t>C004036831</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>C004051583 - IRCANAUPA CONGA JAIME MAMERTO</t>
+          <t>C004036831 - RIVERA AYALA HENY GIOVANA</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -25793,12 +25793,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>C004036831</t>
+          <t>C001763579</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>C004036831 - RIVERA AYALA HENY GIOVANA</t>
+          <t>C001763579 - VILCHEZ HUAMANI IRIS MARLENY</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -25843,7 +25843,7 @@
       </c>
       <c r="Q344" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -25870,12 +25870,12 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>C001763579</t>
+          <t>C004051583</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>C001763579 - VILCHEZ HUAMANI IRIS MARLENY</t>
+          <t>C004051583 - IRCANAUPA CONGA JAIME MAMERTO</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -25920,7 +25920,7 @@
       </c>
       <c r="Q345" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -26154,17 +26154,17 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>C004184768</t>
+          <t>C004188393</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>C004184768 - LLANTOY PARCO RUBIT MARINEZ</t>
+          <t>C004188393 - AQUINO MALLCO FRANCISCA GRACIELA</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H349" s="2" t="n">
@@ -26177,12 +26177,12 @@
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L349" t="inlineStr"/>
@@ -26192,21 +26192,9 @@
         </is>
       </c>
       <c r="N349" t="inlineStr"/>
-      <c r="O349" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P349" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q349" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O349" t="inlineStr"/>
+      <c r="P349" t="inlineStr"/>
+      <c r="Q349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -26231,17 +26219,17 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>C004188393</t>
+          <t>C004184768</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>C004188393 - AQUINO MALLCO FRANCISCA GRACIELA</t>
+          <t>C004184768 - LLANTOY PARCO RUBIT MARINEZ</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H350" s="2" t="n">
@@ -26254,12 +26242,12 @@
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L350" t="inlineStr"/>
@@ -26269,9 +26257,21 @@
         </is>
       </c>
       <c r="N350" t="inlineStr"/>
-      <c r="O350" t="inlineStr"/>
-      <c r="P350" t="inlineStr"/>
-      <c r="Q350" t="inlineStr"/>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -26758,17 +26758,17 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>C004051585</t>
+          <t>C001722569</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>C004051585 - HUAMANI VILCHEZ ERNESTINA</t>
+          <t>C001722569 - CANCHO QUISPE YOVANA</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H357" s="2" t="n">
@@ -26781,12 +26781,12 @@
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="L357" t="inlineStr"/>
@@ -26796,21 +26796,9 @@
         </is>
       </c>
       <c r="N357" t="inlineStr"/>
-      <c r="O357" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P357" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q357" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="O357" t="inlineStr"/>
+      <c r="P357" t="inlineStr"/>
+      <c r="Q357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -26835,17 +26823,17 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>C001722569</t>
+          <t>C004051585</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>C001722569 - CANCHO QUISPE YOVANA</t>
+          <t>C004051585 - HUAMANI VILCHEZ ERNESTINA</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H358" s="2" t="n">
@@ -26858,12 +26846,12 @@
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L358" t="inlineStr"/>
@@ -26873,9 +26861,21 @@
         </is>
       </c>
       <c r="N358" t="inlineStr"/>
-      <c r="O358" t="inlineStr"/>
-      <c r="P358" t="inlineStr"/>
-      <c r="Q358" t="inlineStr"/>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -27350,17 +27350,17 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>C004187738</t>
+          <t>C001743417</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>C004187738 - QUISPE ARANGO GLADYS</t>
+          <t>C001743417 - CRUZ QUISPE MARLENY</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H365" s="2" t="n">
@@ -27373,12 +27373,12 @@
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L365" t="inlineStr"/>
@@ -27388,9 +27388,21 @@
         </is>
       </c>
       <c r="N365" t="inlineStr"/>
-      <c r="O365" t="inlineStr"/>
-      <c r="P365" t="inlineStr"/>
-      <c r="Q365" t="inlineStr"/>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -27415,17 +27427,17 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>C004160273</t>
+          <t>C001749414</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>C004160273 - MIRANDA CANCHO JACINTA</t>
+          <t>C001749414 - CISNEROS PRADO LEYLA MERCEDES</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H366" s="2" t="n">
@@ -27438,12 +27450,12 @@
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L366" t="inlineStr"/>
@@ -27453,9 +27465,21 @@
         </is>
       </c>
       <c r="N366" t="inlineStr"/>
-      <c r="O366" t="inlineStr"/>
-      <c r="P366" t="inlineStr"/>
-      <c r="Q366" t="inlineStr"/>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -27557,17 +27581,17 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>C001749414</t>
+          <t>C004160273</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>C001749414 - CISNEROS PRADO LEYLA MERCEDES</t>
+          <t>C004160273 - MIRANDA CANCHO JACINTA</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H368" s="2" t="n">
@@ -27580,12 +27604,12 @@
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L368" t="inlineStr"/>
@@ -27595,21 +27619,9 @@
         </is>
       </c>
       <c r="N368" t="inlineStr"/>
-      <c r="O368" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P368" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q368" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O368" t="inlineStr"/>
+      <c r="P368" t="inlineStr"/>
+      <c r="Q368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -27634,17 +27646,17 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>C001739552</t>
+          <t>C004187738</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>C001739552 - HUAMAN ZARATE NELY MARILUZ</t>
+          <t>C004187738 - QUISPE ARANGO GLADYS</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H369" s="2" t="n">
@@ -27657,12 +27669,12 @@
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L369" t="inlineStr"/>
@@ -27672,21 +27684,9 @@
         </is>
       </c>
       <c r="N369" t="inlineStr"/>
-      <c r="O369" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P369" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q369" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O369" t="inlineStr"/>
+      <c r="P369" t="inlineStr"/>
+      <c r="Q369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -27711,12 +27711,12 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>C001743417</t>
+          <t>C000922318</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>C001743417 - CRUZ QUISPE MARLENY</t>
+          <t>C000922318 - UCHARIMA TOMA ELADIA</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
@@ -27761,7 +27761,7 @@
       </c>
       <c r="Q370" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -27788,12 +27788,12 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>C000922318</t>
+          <t>C001216674</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>C000922318 - UCHARIMA TOMA ELADIA</t>
+          <t>C001216674 - CHUCHON DE HUAMANI CELEDONIA</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -27838,7 +27838,7 @@
       </c>
       <c r="Q371" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -27865,12 +27865,12 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>C001225339</t>
+          <t>C001383840</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>C001225339 - MENESES YANCE HERLINDA</t>
+          <t>C001383840 - LAPA HUICHO LIDUBINA</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
@@ -27942,12 +27942,12 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>C001383840</t>
+          <t>C001543323</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>C001383840 - LAPA HUICHO LIDUBINA</t>
+          <t>C001543323 - LAHUANA PRADO FLORECINDA</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -28019,12 +28019,12 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>C001216674</t>
+          <t>C001225339</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>C001216674 - CHUCHON DE HUAMANI CELEDONIA</t>
+          <t>C001225339 - MENESES YANCE HERLINDA</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
@@ -28069,7 +28069,7 @@
       </c>
       <c r="Q374" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -28096,17 +28096,17 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>C001543323</t>
+          <t>C001634535</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>C001543323 - LAHUANA PRADO FLORECINDA</t>
+          <t>C001634535 - ROCA TENORIO RUTH ANGELICA</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H375" s="2" t="n">
@@ -28119,12 +28119,12 @@
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L375" t="inlineStr"/>
@@ -28134,21 +28134,9 @@
         </is>
       </c>
       <c r="N375" t="inlineStr"/>
-      <c r="O375" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P375" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q375" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O375" t="inlineStr"/>
+      <c r="P375" t="inlineStr"/>
+      <c r="Q375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -28250,12 +28238,12 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>C001730719</t>
+          <t>C001689150</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>C001730719 - PEREZ DE LA CRUZ ANA</t>
+          <t>C001689150 - ANCHAYHUA HUAMACCTO GABY SILVIA</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
@@ -28300,7 +28288,7 @@
       </c>
       <c r="Q377" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -28327,12 +28315,12 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>C001728928</t>
+          <t>C001672279</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>C001728928 - GALINDO PIZARRO NORMA ISABEL</t>
+          <t>C001672279 - CONDE QUISPE VICENTA</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
@@ -28404,12 +28392,12 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>C001689150</t>
+          <t>C001728928</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>C001689150 - ANCHAYHUA HUAMACCTO GABY SILVIA</t>
+          <t>C001728928 - GALINDO PIZARRO NORMA ISABEL</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
@@ -28454,7 +28442,7 @@
       </c>
       <c r="Q379" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -28481,12 +28469,12 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>C001672279</t>
+          <t>C001730719</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>C001672279 - CONDE QUISPE VICENTA</t>
+          <t>C001730719 - PEREZ DE LA CRUZ ANA</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
@@ -28558,17 +28546,17 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>C001634535</t>
+          <t>C001739552</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>C001634535 - ROCA TENORIO RUTH ANGELICA</t>
+          <t>C001739552 - HUAMAN ZARATE NELY MARILUZ</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H381" s="2" t="n">
@@ -28581,12 +28569,12 @@
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L381" t="inlineStr"/>
@@ -28596,9 +28584,21 @@
         </is>
       </c>
       <c r="N381" t="inlineStr"/>
-      <c r="O381" t="inlineStr"/>
-      <c r="P381" t="inlineStr"/>
-      <c r="Q381" t="inlineStr"/>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P381" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q381" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -28777,17 +28777,17 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>C001626164</t>
+          <t>C001749062</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>C001626164 - COLLAHUACHO GUTIERREZ LUCIA</t>
+          <t>C001749062 - BARZOLA QUISPE YENI CLAUDIA</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H384" s="2" t="n">
@@ -28800,12 +28800,12 @@
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mala Geolocalización</t>
         </is>
       </c>
       <c r="L384" t="inlineStr"/>
@@ -28815,21 +28815,9 @@
         </is>
       </c>
       <c r="N384" t="inlineStr"/>
-      <c r="O384" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P384" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q384" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O384" t="inlineStr"/>
+      <c r="P384" t="inlineStr"/>
+      <c r="Q384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -28854,12 +28842,12 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>C001566424</t>
+          <t>C001626164</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>C001566424 - JERI SOLIER ENMA</t>
+          <t>C001626164 - COLLAHUACHO GUTIERREZ LUCIA</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
@@ -28931,12 +28919,12 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>C001582952</t>
+          <t>C001566424</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>C001582952 - DELGADO MUCHA ROSA</t>
+          <t>C001566424 - JERI SOLIER ENMA</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
@@ -29008,12 +28996,12 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>C001723404</t>
+          <t>C001582952</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>C001723404 - DE LA CRUZ QUISPE ROCIO</t>
+          <t>C001582952 - DELGADO MUCHA ROSA</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
@@ -29085,17 +29073,17 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>C001749062</t>
+          <t>C001723404</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>C001749062 - BARZOLA QUISPE YENI CLAUDIA</t>
+          <t>C001723404 - DE LA CRUZ QUISPE ROCIO</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H388" s="2" t="n">
@@ -29108,12 +29096,12 @@
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>Mala Geolocalización</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L388" t="inlineStr"/>
@@ -29123,9 +29111,21 @@
         </is>
       </c>
       <c r="N388" t="inlineStr"/>
-      <c r="O388" t="inlineStr"/>
-      <c r="P388" t="inlineStr"/>
-      <c r="Q388" t="inlineStr"/>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -29150,12 +29150,12 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>C000922054</t>
+          <t>C001446913</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>C000922054 - AYALA FARFAN LUZ MIRIAN</t>
+          <t>C001446913 - CASTRO MARTINEZ MARISOL</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
@@ -29304,12 +29304,12 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>C001446913</t>
+          <t>C000922054</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>C001446913 - CASTRO MARTINEZ MARISOL</t>
+          <t>C000922054 - AYALA FARFAN LUZ MIRIAN</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
@@ -29523,17 +29523,17 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>C001718826</t>
+          <t>C001744935</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>C001718826 - HUARIPAUCAR MORALES NEMER</t>
+          <t>C001744935 - VENTURA PARIONA PAULINA</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H394" s="2" t="n">
@@ -29546,12 +29546,12 @@
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L394" t="inlineStr"/>
@@ -29561,21 +29561,9 @@
         </is>
       </c>
       <c r="N394" t="inlineStr"/>
-      <c r="O394" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P394" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q394" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O394" t="inlineStr"/>
+      <c r="P394" t="inlineStr"/>
+      <c r="Q394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -29600,12 +29588,12 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>C001732349</t>
+          <t>C001727645</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>C001732349 - LUJAN LIMACO ESTELA</t>
+          <t>C001727645 - ROJAS RODRIGUEZ ROSALI ROXANA</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
@@ -29650,7 +29638,7 @@
       </c>
       <c r="Q395" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -29677,12 +29665,12 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>C001727645</t>
+          <t>C001718826</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>C001727645 - ROJAS RODRIGUEZ ROSALI ROXANA</t>
+          <t>C001718826 - HUARIPAUCAR MORALES NEMER</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
@@ -29819,17 +29807,17 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>C001744935</t>
+          <t>C001732349</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>C001744935 - VENTURA PARIONA PAULINA</t>
+          <t>C001732349 - LUJAN LIMACO ESTELA</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H398" s="2" t="n">
@@ -29842,12 +29830,12 @@
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L398" t="inlineStr"/>
@@ -29857,9 +29845,21 @@
         </is>
       </c>
       <c r="N398" t="inlineStr"/>
-      <c r="O398" t="inlineStr"/>
-      <c r="P398" t="inlineStr"/>
-      <c r="Q398" t="inlineStr"/>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -29884,12 +29884,12 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>C001667509</t>
+          <t>C001670779</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>C001667509 - QUISPE AUCCACUSI DELIA</t>
+          <t>C001670779 - QUICANO ALTAMIRANO ANA MARIA</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
@@ -29934,7 +29934,7 @@
       </c>
       <c r="Q399" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -29961,12 +29961,12 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>C001659449</t>
+          <t>C001667509</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>C001659449 - LOPEZ MACHACCA LOURDES FANNY</t>
+          <t>C001667509 - QUISPE AUCCACUSI DELIA</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
@@ -30011,7 +30011,7 @@
       </c>
       <c r="Q400" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
     </row>
@@ -30103,12 +30103,12 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>C001670779</t>
+          <t>C001659449</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>C001670779 - QUICANO ALTAMIRANO ANA MARIA</t>
+          <t>C001659449 - LOPEZ MACHACCA LOURDES FANNY</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
@@ -30153,7 +30153,7 @@
       </c>
       <c r="Q402" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -30322,17 +30322,17 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>C001482548</t>
+          <t>C001510464</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>C001482548 - YUPARI EVANAN OLGA MARISOL</t>
+          <t>C001510464 - CUYA CISNEROS VICTOR ANDRES</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H405" s="2" t="n">
@@ -30345,12 +30345,12 @@
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L405" t="inlineStr"/>
@@ -30387,17 +30387,17 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>C001510464</t>
+          <t>C004065635</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>C001510464 - CUYA CISNEROS VICTOR ANDRES</t>
+          <t>C004065635 - RUPAY QUISPE YRMA</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H406" s="2" t="n">
@@ -30410,12 +30410,12 @@
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cambio de Giro</t>
         </is>
       </c>
       <c r="L406" t="inlineStr"/>
@@ -30452,17 +30452,17 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>C004065635</t>
+          <t>C004161363</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>C004065635 - RUPAY QUISPE YRMA</t>
+          <t>C004161363 - CEDANO QUISPE PAULINA</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H407" s="2" t="n">
@@ -30475,12 +30475,12 @@
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>Cambio de Giro</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L407" t="inlineStr"/>
@@ -30490,9 +30490,21 @@
         </is>
       </c>
       <c r="N407" t="inlineStr"/>
-      <c r="O407" t="inlineStr"/>
-      <c r="P407" t="inlineStr"/>
-      <c r="Q407" t="inlineStr"/>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>Mejor experiencia con la app</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -30517,12 +30529,12 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>C004161363</t>
+          <t>C001766752</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>C004161363 - CEDANO QUISPE PAULINA</t>
+          <t>C001766752 - YARANGA CONTRERAS YANINA YANETT</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
@@ -30567,7 +30579,7 @@
       </c>
       <c r="Q408" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -30594,12 +30606,12 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>C001766752</t>
+          <t>C000920318</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>C001766752 - YARANGA CONTRERAS YANINA YANETT</t>
+          <t>C000920318 - YANQUI SALAS MARIA MARGARITA</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
@@ -30644,7 +30656,7 @@
       </c>
       <c r="Q409" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -31056,17 +31068,17 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>C000920318</t>
+          <t>C001482548</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>C000920318 - YANQUI SALAS MARIA MARGARITA</t>
+          <t>C001482548 - YUPARI EVANAN OLGA MARISOL</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H415" s="2" t="n">
@@ -31079,12 +31091,12 @@
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K415" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="L415" t="inlineStr"/>
@@ -31094,21 +31106,9 @@
         </is>
       </c>
       <c r="N415" t="inlineStr"/>
-      <c r="O415" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P415" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q415" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="O415" t="inlineStr"/>
+      <c r="P415" t="inlineStr"/>
+      <c r="Q415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -31867,17 +31867,17 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>C001686666</t>
+          <t>C001669740</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>C001686666 - HUAYHUALLA CASTRO WILLIAM EDUARDO</t>
+          <t>C001669740 - JANAMPA GALINDO FLORA</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H426" s="2" t="n">
@@ -31890,12 +31890,12 @@
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L426" t="inlineStr"/>
@@ -31905,9 +31905,21 @@
         </is>
       </c>
       <c r="N426" t="inlineStr"/>
-      <c r="O426" t="inlineStr"/>
-      <c r="P426" t="inlineStr"/>
-      <c r="Q426" t="inlineStr"/>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -31932,12 +31944,12 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>C001669740</t>
+          <t>C001669264</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>C001669740 - JANAMPA GALINDO FLORA</t>
+          <t>C001669264 - DAVALOS PALOMINO EDGAR HERNAN</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
@@ -31982,7 +31994,7 @@
       </c>
       <c r="Q427" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -32009,17 +32021,17 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>C001669264</t>
+          <t>C001686666</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>C001669264 - DAVALOS PALOMINO EDGAR HERNAN</t>
+          <t>C001686666 - HUAYHUALLA CASTRO WILLIAM EDUARDO</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H428" s="2" t="n">
@@ -32032,12 +32044,12 @@
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="L428" t="inlineStr"/>
@@ -32047,21 +32059,9 @@
         </is>
       </c>
       <c r="N428" t="inlineStr"/>
-      <c r="O428" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P428" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q428" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O428" t="inlineStr"/>
+      <c r="P428" t="inlineStr"/>
+      <c r="Q428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -32086,17 +32086,17 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>C001711513</t>
+          <t>C001711514</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>C001711513 - MENESES LUYO KELLY EVANS</t>
+          <t>C001711514 - HURTADO RIVERA ROSA ISABEL</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H429" s="2" t="n">
@@ -32109,12 +32109,12 @@
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No es titular</t>
         </is>
       </c>
       <c r="L429" t="inlineStr"/>
@@ -32124,21 +32124,9 @@
         </is>
       </c>
       <c r="N429" t="inlineStr"/>
-      <c r="O429" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P429" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q429" t="inlineStr">
-        <is>
-          <t>Más capacitación</t>
-        </is>
-      </c>
+      <c r="O429" t="inlineStr"/>
+      <c r="P429" t="inlineStr"/>
+      <c r="Q429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -32163,17 +32151,17 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>C001711514</t>
+          <t>C001711513</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>C001711514 - HURTADO RIVERA ROSA ISABEL</t>
+          <t>C001711513 - MENESES LUYO KELLY EVANS</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H430" s="2" t="n">
@@ -32186,12 +32174,12 @@
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>No es titular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L430" t="inlineStr"/>
@@ -32201,9 +32189,21 @@
         </is>
       </c>
       <c r="N430" t="inlineStr"/>
-      <c r="O430" t="inlineStr"/>
-      <c r="P430" t="inlineStr"/>
-      <c r="Q430" t="inlineStr"/>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>Más capacitación</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -32228,12 +32228,12 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>C001687768</t>
+          <t>C001748093</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>C001687768 - URBINA FLORES MARIA DEL ROSARIO</t>
+          <t>C001748093 - LLAMOCCA QUISPE JUAN</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
@@ -32278,7 +32278,7 @@
       </c>
       <c r="Q431" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -32305,12 +32305,12 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>C001748093</t>
+          <t>C001473641</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>C001748093 - LLAMOCCA QUISPE JUAN</t>
+          <t>C001473641 - QUISPE JANAMPA YUDITH PAOLA</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
@@ -32355,7 +32355,7 @@
       </c>
       <c r="Q432" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -32382,12 +32382,12 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>C001473641</t>
+          <t>C001663297</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>C001473641 - QUISPE JANAMPA YUDITH PAOLA</t>
+          <t>C001663297 - SUAREZ ATAUQUI ZENAIDA</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
@@ -32459,12 +32459,12 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>C001584370</t>
+          <t>C001668200</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>C001584370 - ARESTEGUI CARRASCO MONICA GLADYS</t>
+          <t>C001668200 - LLANTOY HUAMAN MIRIAM MARGOT</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
@@ -32509,7 +32509,7 @@
       </c>
       <c r="Q434" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
     </row>
@@ -32536,12 +32536,12 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>C001663297</t>
+          <t>C001687768</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>C001663297 - SUAREZ ATAUQUI ZENAIDA</t>
+          <t>C001687768 - URBINA FLORES MARIA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
@@ -32613,12 +32613,12 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>C001668200</t>
+          <t>C004182546</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>C001668200 - LLANTOY HUAMAN MIRIAM MARGOT</t>
+          <t>C004182546 - PRADO ROCA EDITH</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
@@ -32690,17 +32690,17 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>C004188982</t>
+          <t>C004188382</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>C004188982 - FERNANDEZ VILLANUEVA NERY</t>
+          <t>C004188382 - ROMERO DE MENDOZA VICTORIA CELSA</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H437" s="2" t="n">
@@ -32713,12 +32713,12 @@
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K437" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No es titular</t>
         </is>
       </c>
       <c r="L437" t="inlineStr"/>
@@ -32728,21 +32728,9 @@
         </is>
       </c>
       <c r="N437" t="inlineStr"/>
-      <c r="O437" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P437" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q437" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="O437" t="inlineStr"/>
+      <c r="P437" t="inlineStr"/>
+      <c r="Q437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -32767,17 +32755,17 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>C004188382</t>
+          <t>C004188982</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>C004188382 - ROMERO DE MENDOZA VICTORIA CELSA</t>
+          <t>C004188982 - FERNANDEZ VILLANUEVA NERY</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H438" s="2" t="n">
@@ -32790,12 +32778,12 @@
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K438" t="inlineStr">
         <is>
-          <t>No es titular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L438" t="inlineStr"/>
@@ -32805,9 +32793,21 @@
         </is>
       </c>
       <c r="N438" t="inlineStr"/>
-      <c r="O438" t="inlineStr"/>
-      <c r="P438" t="inlineStr"/>
-      <c r="Q438" t="inlineStr"/>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -32832,17 +32832,17 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>C004187731</t>
+          <t>C004189005</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>C004187731 - ZAMORA VARGAS OLIVIA</t>
+          <t>C004189005 - TAIPE CRUZ ELIZABETH</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H439" s="2" t="n">
@@ -32855,12 +32855,12 @@
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K439" t="inlineStr">
         <is>
-          <t>Cliente ocupado / ausente</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L439" t="inlineStr"/>
@@ -32870,9 +32870,21 @@
         </is>
       </c>
       <c r="N439" t="inlineStr"/>
-      <c r="O439" t="inlineStr"/>
-      <c r="P439" t="inlineStr"/>
-      <c r="Q439" t="inlineStr"/>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -32897,17 +32909,17 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>C004189005</t>
+          <t>C004189006</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>C004189005 - TAIPE CRUZ ELIZABETH</t>
+          <t>C004189006 - GAMBOA ENCISO ELIANA</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H440" s="2" t="n">
@@ -32920,12 +32932,12 @@
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L440" t="inlineStr"/>
@@ -32935,21 +32947,9 @@
         </is>
       </c>
       <c r="N440" t="inlineStr"/>
-      <c r="O440" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P440" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q440" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="O440" t="inlineStr"/>
+      <c r="P440" t="inlineStr"/>
+      <c r="Q440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -32974,12 +32974,12 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>C004189006</t>
+          <t>C004189011</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>C004189006 - GAMBOA ENCISO ELIANA</t>
+          <t>C004189011 - SAUNE YUPANQUI MAURA NIEVES</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
@@ -33039,12 +33039,12 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>C004189011</t>
+          <t>C004187731</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>C004189011 - SAUNE YUPANQUI MAURA NIEVES</t>
+          <t>C004187731 - ZAMORA VARGAS OLIVIA</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
@@ -33067,7 +33067,7 @@
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>Cliente ocupado / ausente</t>
         </is>
       </c>
       <c r="L442" t="inlineStr"/>
@@ -33104,12 +33104,12 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>C004182546</t>
+          <t>C004186439</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>C004182546 - PRADO ROCA EDITH</t>
+          <t>C004186439 - FLORES ALBITES JUANA</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
@@ -33154,7 +33154,7 @@
       </c>
       <c r="Q443" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
     </row>
@@ -33181,17 +33181,17 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>C004186439</t>
+          <t>C001031427</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>C004186439 - FLORES ALBITES JUANA</t>
+          <t>C001031427 - COLLADO VDA.DE ARCOCCAULLA ALEJANDRA</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H444" s="2" t="n">
@@ -33204,12 +33204,12 @@
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K444" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L444" t="inlineStr"/>
@@ -33219,21 +33219,9 @@
         </is>
       </c>
       <c r="N444" t="inlineStr"/>
-      <c r="O444" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P444" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q444" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="O444" t="inlineStr"/>
+      <c r="P444" t="inlineStr"/>
+      <c r="Q444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -33258,17 +33246,17 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>C001031427</t>
+          <t>C000921781</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>C001031427 - COLLADO VDA.DE ARCOCCAULLA ALEJANDRA</t>
+          <t>C000921781 - MENESES MENDIETA IRMA</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H445" s="2" t="n">
@@ -33281,12 +33269,12 @@
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K445" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L445" t="inlineStr"/>
@@ -33296,9 +33284,21 @@
         </is>
       </c>
       <c r="N445" t="inlineStr"/>
-      <c r="O445" t="inlineStr"/>
-      <c r="P445" t="inlineStr"/>
-      <c r="Q445" t="inlineStr"/>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -33323,17 +33323,17 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>C000921781</t>
+          <t>C000921477</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>C000921781 - MENESES MENDIETA IRMA</t>
+          <t>C000921477 - AYALA VASQUEZ ADELAIDA EMILIANA</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H446" s="2" t="n">
@@ -33346,12 +33346,12 @@
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="K446" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PDV Cerrado</t>
         </is>
       </c>
       <c r="L446" t="inlineStr"/>
@@ -33361,21 +33361,9 @@
         </is>
       </c>
       <c r="N446" t="inlineStr"/>
-      <c r="O446" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="P446" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="Q446" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="O446" t="inlineStr"/>
+      <c r="P446" t="inlineStr"/>
+      <c r="Q446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -33400,17 +33388,17 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>C000921477</t>
+          <t>C001219345</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>C000921477 - AYALA VASQUEZ ADELAIDA EMILIANA</t>
+          <t>C001219345 - ALVITEZ TACO IRMA</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="H447" s="2" t="n">
@@ -33423,12 +33411,12 @@
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="K447" t="inlineStr">
         <is>
-          <t>PDV Cerrado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L447" t="inlineStr"/>
@@ -33438,9 +33426,21 @@
         </is>
       </c>
       <c r="N447" t="inlineStr"/>
-      <c r="O447" t="inlineStr"/>
-      <c r="P447" t="inlineStr"/>
-      <c r="Q447" t="inlineStr"/>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>C001219345</t>
+          <t>C001217185</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>C001219345 - ALVITEZ TACO IRMA</t>
+          <t>C001217185 - HUARANCCA GARCIA OLGA</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
@@ -33542,12 +33542,12 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>C001217185</t>
+          <t>C001491694</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>C001217185 - HUARANCCA GARCIA OLGA</t>
+          <t>C001491694 - SOTACURO MUÑOZ ALBINA</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
@@ -33592,7 +33592,7 @@
       </c>
       <c r="Q449" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
     </row>
@@ -33619,12 +33619,12 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>C001491694</t>
+          <t>C001584370</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>C001491694 - SOTACURO MUÑOZ ALBINA</t>
+          <t>C001584370 - ARESTEGUI CARRASCO MONICA GLADYS</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
